--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingAccessoriesData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingAccessoriesData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8537CA5-2C3C-4BC7-9573-581A5017D141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EB94B4-1E30-460C-A986-BB044F9C8AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="7450" windowWidth="26690" windowHeight="12250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3130" yWindow="1270" windowWidth="26660" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -101,6 +101,31 @@
   <si>
     <t>220005+1/220006+1/220007+1</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AccessoriesIconName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>图标名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accessories_01.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accessories_02.png</t>
+  </si>
+  <si>
+    <t>Accessories_03.png</t>
+  </si>
+  <si>
+    <t>Accessories_04.png</t>
   </si>
 </sst>
 </file>
@@ -177,7 +202,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -459,15 +484,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="43.1640625" customWidth="1"/>
-    <col min="4" max="4" width="35.58203125" customWidth="1"/>
-    <col min="5" max="5" width="49.75" customWidth="1"/>
+    <col min="3" max="4" width="43.1640625" customWidth="1"/>
+    <col min="5" max="5" width="35.58203125" customWidth="1"/>
+    <col min="6" max="6" width="49.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -478,10 +503,13 @@
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -491,11 +519,14 @@
       <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -506,50 +537,65 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>10001</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>10002</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>10003</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>10004</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>16</v>
       </c>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingAccessoriesData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingAccessoriesData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EB94B4-1E30-460C-A986-BB044F9C8AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6C027B-89A5-422F-858B-147A4354CEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3130" yWindow="1270" windowWidth="26660" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -126,6 +126,41 @@
   </si>
   <si>
     <t>Accessories_04.png</t>
+  </si>
+  <si>
+    <t>PcbSlotList</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=+),long</t>
+  </si>
+  <si>
+    <t>剪裁槽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1+1+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1+2+3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1+3+3+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1+1+1+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AccessoriesDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配件多语言Key描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -484,15 +519,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="4" width="43.1640625" customWidth="1"/>
-    <col min="5" max="5" width="35.58203125" customWidth="1"/>
-    <col min="6" max="6" width="49.75" customWidth="1"/>
+    <col min="3" max="5" width="43.1640625" customWidth="1"/>
+    <col min="6" max="6" width="35.58203125" customWidth="1"/>
+    <col min="7" max="7" width="49.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -503,13 +538,19 @@
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -520,13 +561,19 @@
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -537,13 +584,19 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="G3" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>10001</v>
       </c>
@@ -551,13 +604,19 @@
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="G4" s="1" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>10002</v>
       </c>
@@ -565,13 +624,19 @@
         <v>9</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="G5" s="1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>10003</v>
       </c>
@@ -579,13 +644,19 @@
         <v>10</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="G6" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="7" spans="1:5" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>10004</v>
       </c>
@@ -593,10 +664,16 @@
         <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>16</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingAccessoriesData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingAccessoriesData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6C027B-89A5-422F-858B-147A4354CEFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A249E25-A5FC-437E-A14C-33450286E0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3130" yWindow="1270" windowWidth="26660" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2500" windowWidth="37150" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -160,6 +160,14 @@
   </si>
   <si>
     <t>配件多语言Key描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AccessoriesMaxIconName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accessories_0999.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -519,15 +527,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="5" width="43.1640625" customWidth="1"/>
-    <col min="6" max="6" width="35.58203125" customWidth="1"/>
-    <col min="7" max="7" width="49.75" customWidth="1"/>
+    <col min="3" max="6" width="43.1640625" customWidth="1"/>
+    <col min="7" max="7" width="35.58203125" customWidth="1"/>
+    <col min="8" max="8" width="49.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -544,13 +552,16 @@
         <v>17</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="16.5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -566,14 +577,17 @@
       <c r="E2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -590,13 +604,16 @@
         <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
         <v>10001</v>
       </c>
@@ -607,16 +624,19 @@
         <v>8</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>10002</v>
       </c>
@@ -627,16 +647,19 @@
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>10003</v>
       </c>
@@ -647,16 +670,19 @@
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>10004</v>
       </c>
@@ -667,12 +693,15 @@
         <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>30</v>
       </c>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/ClothingAccessoriesData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/ClothingAccessoriesData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A249E25-A5FC-437E-A14C-33450286E0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{192E5028-1324-40DC-9EDE-269EAA58ED75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2500" windowWidth="37150" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="37160" windowHeight="17840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="52">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -115,60 +115,118 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Accessories_02.png</t>
+  </si>
+  <si>
+    <t>Accessories_03.png</t>
+  </si>
+  <si>
+    <t>Accessories_04.png</t>
+  </si>
+  <si>
+    <t>PcbSlotList</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(list#sep=+),long</t>
+  </si>
+  <si>
+    <t>剪裁槽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1+1+2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1+2+3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1+3+3+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1+1+1+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AccessoriesDesc</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配件多语言Key描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AccessoriesMaxIconName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accessories_0999.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Remark</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>耳朵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尾巴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手臂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胸部</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配饰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>靴子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClothingAccessories+ClothingAccessories_05</t>
+  </si>
+  <si>
+    <t>ClothingAccessories+ClothingAccessories_06</t>
+  </si>
+  <si>
+    <t>Accessories_05.png</t>
+  </si>
+  <si>
+    <t>220005+1/220006+1/220007+2</t>
+  </si>
+  <si>
+    <t>220005+1/220006+1/220007+3</t>
+  </si>
+  <si>
+    <t>1+1+1+2</t>
+  </si>
+  <si>
+    <t>1+1+1+3</t>
+  </si>
+  <si>
+    <t>Accessories_00.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Accessories_01.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accessories_02.png</t>
-  </si>
-  <si>
-    <t>Accessories_03.png</t>
-  </si>
-  <si>
-    <t>Accessories_04.png</t>
-  </si>
-  <si>
-    <t>PcbSlotList</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(list#sep=+),long</t>
-  </si>
-  <si>
-    <t>剪裁槽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1+1+2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1+2+3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1+3+3+1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1+1+1+1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AccessoriesDesc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配件多语言Key描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AccessoriesMaxIconName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accessories_0999.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -527,15 +585,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="6" width="43.1640625" customWidth="1"/>
-    <col min="7" max="7" width="35.58203125" customWidth="1"/>
-    <col min="8" max="8" width="49.75" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="7" width="43.1640625" customWidth="1"/>
+    <col min="8" max="8" width="35.58203125" customWidth="1"/>
+    <col min="9" max="9" width="49.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -543,167 +602,246 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="16.5" x14ac:dyDescent="0.4">
+      <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
+      <c r="C2" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="I3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B4" s="1">
-        <v>10001</v>
+        <v>10000</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="I4" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="I5" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="I6" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="I7" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B8" s="1">
+        <v>10004</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B9" s="1">
+        <v>10005</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="F11" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
